--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,5%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,47 +816,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +885,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,47 +966,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1035,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>52</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,7 +1117,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1143,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1181,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1254,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,51 +1262,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,33 +1327,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>49</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,11 +1409,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,33 +1473,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,6%</t>
+        <v>33</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,11 +1555,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1615,33 +1619,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,7 +1692,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1696,47 +1700,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1761,33 +1769,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1843,7 +1851,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1877,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,33 +1915,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>63</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1943,19 +1951,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2016,19 +2024,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2056,22 +2064,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2079,7 +2087,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2089,19 +2097,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2137,9 +2145,9 @@
       <c r="I23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2162,19 +2170,19 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,33 +2207,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2235,19 +2243,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,7 +2280,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,10 +2288,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2292,39 +2298,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,33 +2353,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,4%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2433,9 +2437,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2465,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2504,16 +2508,16 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>102</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2521,7 +2525,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2538,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2577,7 +2581,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2611,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2650,16 +2654,16 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>93</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2684,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2761,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2800,16 +2804,16 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>121</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2817,7 +2821,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2864,7 +2868,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2872,10 +2876,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2884,39 +2886,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2950,16 +2950,16 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3022,10 +3022,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3034,39 +3032,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3100,11 +3096,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3117,7 +3113,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3134,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3211,12 +3207,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3250,16 +3246,16 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>80</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3267,7 +3263,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3284,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3361,12 +3357,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3394,22 +3390,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3417,7 +3413,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3434,12 +3430,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3511,12 +3507,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3541,33 +3537,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>89</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3584,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3661,12 +3657,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3696,20 +3692,20 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,4%</t>
+        <v>65</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3717,7 +3713,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3734,12 +3730,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3811,12 +3807,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3841,20 +3837,20 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3863,11 +3859,11 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3884,12 +3880,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3961,12 +3957,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3991,33 +3987,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4034,12 +4030,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4111,12 +4107,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4150,16 +4146,16 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>48</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4167,7 +4163,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4184,12 +4180,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4261,12 +4257,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4294,17 +4290,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4334,12 +4330,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4411,12 +4407,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4441,33 +4437,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,2%</t>
+        <v>36</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4484,12 +4480,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4561,12 +4557,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4591,33 +4587,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4634,12 +4630,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4711,12 +4707,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4741,33 +4737,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>64</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4784,12 +4780,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4861,12 +4857,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4891,33 +4887,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4934,12 +4930,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5011,12 +5007,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5041,25 +5037,25 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>49</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5067,7 +5063,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5084,12 +5080,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5161,12 +5157,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5191,33 +5187,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,0%</t>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5234,12 +5230,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5311,12 +5307,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5341,33 +5337,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 201,4%</t>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>44</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5384,12 +5380,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5461,12 +5457,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5500,7 +5496,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5509,7 +5505,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5517,7 +5513,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5534,12 +5530,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5611,12 +5607,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5646,20 +5642,20 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>32</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5684,12 +5680,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5761,12 +5757,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5791,33 +5787,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,1%</t>
+        <v>33</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5834,12 +5830,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5911,12 +5907,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5944,22 +5940,22 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>42</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5984,12 +5980,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6061,12 +6057,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6091,33 +6087,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>42</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6134,82 +6130,532 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,0%</t>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -828,41 +826,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -888,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1005,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1035,33 +1031,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,5%</t>
+        <v>70</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1078,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,8 +1112,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1126,39 +1124,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1184,22 +1184,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>52</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1265,9 +1265,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1297,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1327,33 +1327,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,14 +1370,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1409,11 +1409,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1443,14 +1443,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1482,24 +1482,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1516,14 +1516,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1555,11 +1555,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1589,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1622,17 +1622,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1662,14 +1662,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1700,10 +1700,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1712,41 +1710,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1769,33 +1765,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,14 +1808,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1842,7 +1838,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1850,8 +1846,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1860,39 +1858,41 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1915,33 +1915,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,6%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1999,9 +1999,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,14 +2031,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2061,33 +2061,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,0%</t>
+        <v>63</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,14 +2177,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2210,22 +2210,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>87</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2289,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,14 +2323,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2353,33 +2353,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>77</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2389,21 +2389,21 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2435,11 +2435,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2462,21 +2462,21 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2499,33 +2499,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,14 +2542,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2581,11 +2581,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2615,14 +2615,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2645,33 +2645,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>102</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,14 +2688,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2726,10 +2726,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2738,41 +2736,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2795,33 +2791,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+        <v>93</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2838,14 +2834,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2868,7 +2864,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2876,8 +2872,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2886,39 +2884,41 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2944,22 +2944,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>121</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3057,14 +3057,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3087,33 +3087,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>81</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3130,14 +3130,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3168,10 +3168,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3180,41 +3178,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3237,33 +3233,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>87</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3280,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3357,14 +3353,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3390,22 +3386,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3413,7 +3409,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3430,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3507,14 +3503,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3537,33 +3533,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+        <v>84</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3580,12 +3576,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3657,14 +3653,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3687,33 +3683,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>89</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3730,12 +3726,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3807,14 +3803,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3846,7 +3842,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3855,7 +3851,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3863,7 +3859,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3880,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3957,12 +3953,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3998,9 +3994,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4013,7 +4009,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4030,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4107,14 +4103,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4142,20 +4138,20 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4163,7 +4159,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4180,12 +4176,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4257,14 +4253,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4287,33 +4283,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>48</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4330,12 +4326,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4407,14 +4403,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4437,33 +4433,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>67</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4480,12 +4476,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4557,14 +4553,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4587,33 +4583,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>36</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4630,12 +4626,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4707,14 +4703,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4737,7 +4733,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4746,24 +4742,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4780,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4857,14 +4853,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4890,17 +4886,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,2%</t>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4930,12 +4926,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5007,14 +5003,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5037,33 +5033,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5080,12 +5076,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5157,14 +5153,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5187,33 +5183,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>49</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5230,12 +5226,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5307,14 +5303,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5337,33 +5333,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,8%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5380,12 +5376,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5457,14 +5453,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5487,25 +5483,25 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>44</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5513,7 +5509,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5530,12 +5526,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5607,14 +5603,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5640,17 +5636,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5680,12 +5676,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5757,14 +5753,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5787,33 +5783,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,4%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5830,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5907,14 +5903,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5937,33 +5933,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>33</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5980,12 +5976,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6057,14 +6053,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6090,17 +6086,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6113,7 +6109,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6130,12 +6126,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6207,14 +6203,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6237,33 +6233,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6280,12 +6276,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6357,14 +6353,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6387,33 +6383,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>36</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6430,12 +6426,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6507,14 +6503,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6537,33 +6533,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6580,82 +6576,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,8%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,0%</t>
+        <v>54</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,51 +962,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>41</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,51 +1108,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1181,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,5%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1224,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1263,7 +1255,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1297,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1408,47 +1400,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1473,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1516,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1546,7 +1542,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1554,47 +1550,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1619,33 +1619,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>52</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1765,33 +1765,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1846,51 +1846,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,33 +1911,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>49</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1997,11 +1993,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,33 +2057,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,6%</t>
+        <v>33</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2143,11 +2139,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,33 +2203,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2280,7 +2276,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2288,47 +2284,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,33 +2353,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2469,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2499,33 +2499,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>63</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2608,19 +2608,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2648,22 +2648,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2681,19 +2681,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2729,9 +2729,9 @@
       <c r="I31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2791,33 +2791,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2827,19 +2827,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2872,10 +2872,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2884,39 +2882,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2941,33 +2937,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,4%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3025,9 +3021,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3057,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3096,16 +3092,16 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>102</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3113,7 +3109,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3130,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3169,7 +3165,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3203,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3242,16 +3238,16 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>93</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3259,7 +3255,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3276,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3353,12 +3349,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3392,16 +3388,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>121</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3409,7 +3405,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3426,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3456,7 +3452,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3464,10 +3460,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3476,39 +3470,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3542,16 +3534,16 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3559,7 +3551,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3576,12 +3568,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3606,7 +3598,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3614,10 +3606,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3626,39 +3616,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3692,11 +3680,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3709,7 +3697,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3726,12 +3714,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3803,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3842,16 +3830,16 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>80</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3859,7 +3847,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3876,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3953,12 +3941,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3986,22 +3974,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4009,7 +3997,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4026,12 +4014,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4103,12 +4091,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4133,33 +4121,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>89</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4176,12 +4164,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4253,12 +4241,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4288,20 +4276,20 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,4%</t>
+        <v>65</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4309,7 +4297,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4326,12 +4314,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4403,12 +4391,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4433,20 +4421,20 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4455,11 +4443,11 @@
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4476,12 +4464,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4553,12 +4541,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4583,33 +4571,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4626,12 +4614,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,12 +4691,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4742,16 +4730,16 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>48</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4759,7 +4747,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4776,12 +4764,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4853,12 +4841,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4886,17 +4874,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4926,12 +4914,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5003,12 +4991,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5033,33 +5021,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,2%</t>
+        <v>36</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5076,12 +5064,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5153,12 +5141,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5183,33 +5171,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5226,12 +5214,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5303,12 +5291,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5333,33 +5321,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>64</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5376,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5453,12 +5441,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5483,33 +5471,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5526,12 +5514,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5603,12 +5591,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5633,25 +5621,25 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>49</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5659,7 +5647,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5676,12 +5664,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5753,12 +5741,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5783,33 +5771,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,0%</t>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5826,12 +5814,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5903,12 +5891,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5933,33 +5921,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 201,4%</t>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>44</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5976,12 +5964,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6053,12 +6041,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6092,7 +6080,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6101,7 +6089,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6109,7 +6097,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6126,12 +6114,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6203,12 +6191,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6238,20 +6226,20 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>32</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6276,12 +6264,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6353,12 +6341,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6383,33 +6371,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,1%</t>
+        <v>33</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6426,12 +6414,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6503,12 +6491,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6536,22 +6524,22 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>42</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6576,12 +6564,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6653,12 +6641,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6683,33 +6671,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>42</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6726,82 +6714,532 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+        <v>45</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,22 +738,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+        <v>35</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,8%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,0%</t>
+        <v>54</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1400,51 +1400,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>41</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1542,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1550,51 +1546,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1619,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,5%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1662,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1701,7 +1693,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1735,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1765,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1808,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1838,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1846,47 +1838,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1911,33 +1907,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1954,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1984,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1992,47 +1988,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2057,33 +2057,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>52</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2173,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2203,33 +2203,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2284,51 +2284,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,33 +2349,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>49</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2435,11 +2431,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2499,33 +2495,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,6%</t>
+        <v>33</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2581,11 +2577,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2615,12 +2611,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2645,33 +2641,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,12 +2684,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2718,7 +2714,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2726,47 +2722,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2791,33 +2791,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2937,33 +2937,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>63</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2973,19 +2973,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3046,19 +3046,19 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3086,22 +3086,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3119,19 +3119,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3167,9 +3167,9 @@
       <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3192,19 +3192,19 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3229,33 +3229,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3265,19 +3265,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3310,10 +3310,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3322,39 +3320,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3379,33 +3375,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,4%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3422,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3463,9 +3459,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3495,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3534,16 +3530,16 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>102</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3551,7 +3547,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3568,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3607,7 +3603,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3641,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3680,16 +3676,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>93</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3697,7 +3693,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3714,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3791,12 +3787,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3830,16 +3826,16 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>121</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3847,7 +3843,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3864,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3894,7 +3890,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3902,10 +3898,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3914,39 +3908,37 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3980,16 +3972,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3997,7 +3989,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4014,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4044,7 +4036,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4052,10 +4044,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4064,39 +4054,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4130,11 +4118,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4147,7 +4135,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4164,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4241,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4280,16 +4268,16 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>80</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4297,7 +4285,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4314,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,12 +4379,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4424,22 +4412,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4447,7 +4435,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4464,12 +4452,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4541,12 +4529,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4571,33 +4559,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>89</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4614,12 +4602,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4691,12 +4679,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4726,20 +4714,20 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,4%</t>
+        <v>65</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4747,7 +4735,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4764,12 +4752,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4841,12 +4829,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4871,20 +4859,20 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4893,11 +4881,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4914,12 +4902,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4991,12 +4979,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5021,33 +5009,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5064,12 +5052,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5141,12 +5129,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5180,16 +5168,16 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>48</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5197,7 +5185,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5214,12 +5202,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5291,12 +5279,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5324,17 +5312,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5364,12 +5352,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5441,12 +5429,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5471,33 +5459,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,2%</t>
+        <v>36</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5514,12 +5502,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5591,12 +5579,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5621,33 +5609,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,12 +5652,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5741,12 +5729,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5771,33 +5759,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>64</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5814,12 +5802,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5891,12 +5879,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5921,33 +5909,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,12 +5952,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6041,12 +6029,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6071,25 +6059,25 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>49</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6097,7 +6085,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6114,12 +6102,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6191,12 +6179,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6221,33 +6209,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,0%</t>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6264,12 +6252,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6341,12 +6329,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6371,33 +6359,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 201,4%</t>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>44</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6414,12 +6402,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6491,12 +6479,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6530,7 +6518,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6539,7 +6527,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6547,7 +6535,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6564,12 +6552,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6641,12 +6629,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6676,20 +6664,20 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>32</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6714,12 +6702,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6791,12 +6779,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6821,33 +6809,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,1%</t>
+        <v>33</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6864,12 +6852,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6941,12 +6929,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6974,22 +6962,22 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>42</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -7014,12 +7002,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7091,12 +7079,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7121,33 +7109,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>42</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7164,82 +7152,532 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>56</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,4%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -738,22 +738,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>45</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+        <v>35</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,2%</t>
+        <v>31</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+        <v>54</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,8%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1620,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,0%</t>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1838,10 +1838,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1850,41 +1848,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1910,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2027,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2057,33 +2053,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,5%</t>
+        <v>70</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2100,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2130,7 +2126,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2138,8 +2134,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2148,39 +2146,41 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2206,22 +2206,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>52</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2287,9 +2287,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2319,14 +2319,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2349,33 +2349,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,14 +2392,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2431,11 +2431,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2465,14 +2465,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2504,24 +2504,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2538,14 +2538,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2577,11 +2577,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2611,14 +2611,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2644,17 +2644,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2684,14 +2684,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2722,10 +2722,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2734,41 +2732,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2791,33 +2787,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2864,7 +2860,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2872,8 +2868,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2882,39 +2880,41 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2937,33 +2937,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,6%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3021,9 +3021,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3053,14 +3053,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3083,33 +3083,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,0%</t>
+        <v>63</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3126,14 +3126,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3165,11 +3165,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3199,14 +3199,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3232,22 +3232,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>87</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3272,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3311,11 +3311,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3345,14 +3345,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3375,33 +3375,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>77</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3411,21 +3411,21 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3484,21 +3484,21 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3521,33 +3521,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3603,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3667,33 +3667,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>102</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3710,14 +3710,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3748,10 +3748,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3760,41 +3758,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3817,33 +3813,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+        <v>93</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3860,14 +3856,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3890,7 +3886,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3898,8 +3894,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3908,39 +3906,41 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3966,22 +3966,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>121</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4079,14 +4079,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4109,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>81</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4152,14 +4152,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4190,10 +4190,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4202,41 +4200,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4259,33 +4255,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>87</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4302,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4379,14 +4375,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4412,22 +4408,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4435,7 +4431,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4452,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4529,14 +4525,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4559,33 +4555,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+        <v>84</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4602,12 +4598,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4679,14 +4675,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4709,33 +4705,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>89</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4752,12 +4748,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4829,14 +4825,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4868,7 +4864,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4877,7 +4873,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4885,7 +4881,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4902,12 +4898,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4979,12 +4975,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5020,9 +5016,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5035,7 +5031,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5052,12 +5048,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5129,14 +5125,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5164,20 +5160,20 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5185,7 +5181,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5202,12 +5198,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5279,14 +5275,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5309,33 +5305,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>48</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5352,12 +5348,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5429,14 +5425,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5459,33 +5455,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>67</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5502,12 +5498,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5579,14 +5575,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5609,33 +5605,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>36</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5652,12 +5648,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5729,14 +5725,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5759,7 +5755,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5768,24 +5764,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5802,12 +5798,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5879,14 +5875,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5912,17 +5908,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,2%</t>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5952,12 +5948,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6029,14 +6025,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6059,33 +6055,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6102,12 +6098,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6179,14 +6175,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6209,33 +6205,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>49</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6252,12 +6248,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6329,14 +6325,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6359,33 +6355,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,8%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6402,12 +6398,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6479,14 +6475,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6509,25 +6505,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>44</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6535,7 +6531,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6552,12 +6548,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6629,14 +6625,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6662,17 +6658,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6702,12 +6698,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6779,14 +6775,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6809,33 +6805,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,4%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6852,12 +6848,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6929,14 +6925,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6959,33 +6955,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>33</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7002,12 +6998,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7079,14 +7075,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7112,17 +7108,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7135,7 +7131,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7152,12 +7148,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7229,14 +7225,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7259,33 +7255,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7302,12 +7298,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7379,14 +7375,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7409,33 +7405,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>36</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7452,12 +7448,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7529,14 +7525,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7559,33 +7555,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7602,82 +7598,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,4%</t>
+        <v>46</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,22 +738,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>43</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,47 +816,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +885,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 24,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +967,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1031,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>45</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1113,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1259,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1332,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,2%</t>
+        <v>35</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1405,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,7 +1472,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1476,9 +1480,9 @@
       <c r="I14" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1551,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1624,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,8%</t>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1727,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,17 +1764,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1907,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,24 +1916,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>41</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1984,51 +1988,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2056,17 +2056,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,6%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2134,10 +2134,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2146,39 +2144,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2203,33 +2199,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,5%</t>
+        <v>53</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2246,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,7 +2272,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2284,8 +2280,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2294,37 +2292,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,33 +2349,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>70</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2430,47 +2430,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2495,33 +2499,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2538,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2577,11 +2581,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2611,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2641,33 +2645,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>63</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2684,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2723,11 +2727,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2757,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2787,33 +2791,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>49</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2830,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2860,7 +2864,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2868,51 +2872,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2937,33 +2937,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3083,33 +3083,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,6%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3164,47 +3164,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3229,33 +3233,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3272,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3311,11 +3315,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3345,12 +3349,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3375,33 +3379,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>63</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3418,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3457,11 +3461,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3491,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3521,33 +3525,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>87</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3557,19 +3561,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3603,11 +3607,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3630,19 +3634,19 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3672,20 +3676,20 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3693,7 +3697,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3703,19 +3707,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3749,7 +3753,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3776,19 +3780,19 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3813,33 +3817,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3856,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3886,7 +3890,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3894,51 +3898,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3966,22 +3966,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+        <v>102</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4079,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4109,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>93</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4190,8 +4190,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4200,37 +4202,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4255,33 +4259,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>121</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4298,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4328,7 +4332,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4336,10 +4340,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4348,39 +4350,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4408,17 +4408,17 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>81</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4486,10 +4486,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4498,39 +4496,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4555,33 +4551,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4598,12 +4594,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4675,12 +4671,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4705,33 +4701,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4748,12 +4744,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4825,12 +4821,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4858,22 +4854,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>84</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4881,7 +4877,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4898,12 +4894,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4975,12 +4971,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5005,33 +5001,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>89</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5048,12 +5044,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5125,12 +5121,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5164,16 +5160,16 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>65</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5181,7 +5177,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5198,12 +5194,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5275,12 +5271,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5310,20 +5306,20 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5331,7 +5327,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5348,12 +5344,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5425,12 +5421,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5455,33 +5451,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
-        </is>
-      </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5498,12 +5494,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5575,12 +5571,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5605,33 +5601,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>48</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5648,12 +5644,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5725,12 +5721,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5755,33 +5751,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>67</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5798,12 +5794,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5875,12 +5871,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5905,33 +5901,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5948,12 +5944,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6025,12 +6021,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6055,33 +6051,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,2%</t>
+        <v>65</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6098,12 +6094,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6175,12 +6171,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6205,33 +6201,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 44,1%</t>
+        <v>64</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6248,12 +6244,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6325,12 +6321,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6355,33 +6351,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,7%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6398,12 +6394,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6475,12 +6471,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6510,20 +6506,20 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,8%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>49</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6531,7 +6527,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,12 +6544,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6625,12 +6621,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6655,33 +6651,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>34</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6698,12 +6694,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6775,12 +6771,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6805,25 +6801,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,8%</t>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 3,0%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6831,7 +6827,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6848,12 +6844,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6925,12 +6921,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6955,33 +6951,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,4%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>32</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6998,12 +6994,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7075,12 +7071,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7108,22 +7104,22 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7131,7 +7127,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7148,12 +7144,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7225,12 +7221,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7255,33 +7251,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
+          <t>R$ 223,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7298,12 +7294,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7375,12 +7371,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7405,33 +7401,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,1%</t>
+        <v>42</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7448,12 +7444,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7525,12 +7521,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7558,22 +7554,22 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7581,7 +7577,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7598,12 +7594,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7675,12 +7671,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7705,33 +7701,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>36</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7748,82 +7744,382 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,0%</t>
+          <t>▼ 14,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -698,19 +698,19 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 631,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,2%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -828,39 +826,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,4%</t>
+        <v>80</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1034,22 +1030,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>62</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1057,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,47 +1108,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,33 +1323,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>68</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,6%</t>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1550,47 +1550,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1615,7 +1619,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1624,24 +1628,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▲ 74,2%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1697,11 +1701,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1731,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1764,17 +1768,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+        <v>54</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1843,11 +1847,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1877,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,33 +1911,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,8%</t>
+        <v>57</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,1%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2053,33 +2057,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 17,0%</t>
+          <t>▲ 19,2%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2135,11 +2139,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,33 +2203,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2242,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,7 +2276,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,51 +2284,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,33 +2349,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>46</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2430,10 +2430,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2442,39 +2440,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2499,33 +2495,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,5%</t>
+        <v>43</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,2%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2572,7 +2568,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2580,8 +2576,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2590,37 +2588,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2648,22 +2648,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>56</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2688,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2729,9 +2729,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2796,20 +2796,20 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+        <v>45</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2937,20 +2937,20 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2959,11 +2959,11 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3021,9 +3021,9 @@
       <c r="I35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3083,33 +3083,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>35</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3164,10 +3164,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3176,39 +3174,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3233,33 +3229,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>31</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3276,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3317,9 +3313,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3349,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3379,33 +3375,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 27,6%</t>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3422,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3461,11 +3457,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3495,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3525,33 +3521,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3568,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3609,9 +3605,9 @@
       <c r="I43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3641,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3671,33 +3667,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>41</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3714,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3753,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3787,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3817,33 +3813,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,8%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3853,19 +3849,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3899,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3926,19 +3922,19 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3963,33 +3959,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3999,19 +3995,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4036,7 +4032,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4044,8 +4040,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4054,37 +4052,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4109,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4145,19 +4145,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4268,24 +4268,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,4%</t>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4295,19 +4295,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4368,19 +4368,19 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4405,33 +4405,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,9%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4441,19 +4441,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4489,9 +4489,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4514,19 +4514,19 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4551,33 +4551,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>49</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4587,19 +4587,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4632,51 +4632,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4701,33 +4697,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▼ 4,8%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4737,19 +4733,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4782,10 +4778,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4794,39 +4788,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4851,33 +4843,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4887,19 +4879,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4971,12 +4963,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5001,33 +4993,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,9%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5037,19 +5029,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5074,7 +5066,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5082,10 +5074,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5094,39 +5084,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5151,33 +5139,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>63</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5187,19 +5175,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5224,7 +5212,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5232,51 +5220,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5310,16 +5294,16 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>87</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5327,7 +5311,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5337,19 +5321,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5374,7 +5358,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5382,51 +5366,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5454,22 +5434,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>77</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5477,7 +5457,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5487,19 +5467,19 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5524,7 +5504,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5532,10 +5512,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5544,39 +5522,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5601,33 +5577,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,4%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5644,12 +5620,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5674,7 +5650,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5682,51 +5658,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5751,33 +5723,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>102</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5794,12 +5766,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5824,7 +5796,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5832,10 +5804,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5844,39 +5814,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5901,29 +5869,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>93</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5944,12 +5912,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6021,12 +5989,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6056,20 +6024,20 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>121</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6077,7 +6045,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6094,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6124,7 +6092,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6132,10 +6100,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6144,39 +6110,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6201,33 +6165,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6244,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6274,7 +6238,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6282,10 +6246,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6294,39 +6256,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6351,33 +6311,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,2%</t>
+        <v>87</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6394,12 +6354,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6471,12 +6431,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6501,33 +6461,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6544,12 +6504,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6621,12 +6581,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6651,33 +6611,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>84</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,12 +6654,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6771,12 +6731,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6801,33 +6761,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,8%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>89</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6844,12 +6804,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6921,12 +6881,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6951,7 +6911,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6960,11 +6920,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6973,11 +6933,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6994,12 +6954,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7071,12 +7031,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7101,33 +7061,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 3,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7144,12 +7104,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7221,12 +7181,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7251,33 +7211,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▲ 201,4%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7294,12 +7254,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7371,12 +7331,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7401,33 +7361,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>48</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7444,12 +7404,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7521,12 +7481,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7551,33 +7511,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>67</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7594,12 +7554,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7671,12 +7631,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7701,12 +7661,12 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
@@ -7714,20 +7674,20 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,1%</t>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7744,12 +7704,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7821,12 +7781,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7851,33 +7811,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▼ 12,1%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7894,12 +7854,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7971,12 +7931,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8001,7 +7961,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8010,24 +7970,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>64</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8044,82 +8004,1882 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,2%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,7%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,8%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,4%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">

--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -742,17 +742,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,24 +1048,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 118,8%</t>
+        <v>13</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>35</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 118,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1492,17 +1492,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1944,20 +1944,20 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,3%</t>
+        <v>77</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2089,33 +2089,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+        <v>54</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2239,33 +2239,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 390,9%</t>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2394,20 +2394,20 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>54</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 390,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2547,10 +2547,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2559,39 +2557,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2663,14 +2659,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2693,7 +2689,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2701,8 +2697,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2711,37 +2709,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,14 +2813,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2851,10 +2851,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2863,39 +2861,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2967,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3044,12 +3040,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3121,12 +3117,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3198,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3275,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3352,12 +3348,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3429,14 +3425,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3459,7 +3455,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3467,8 +3463,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3477,37 +3475,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3579,14 +3579,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3612,17 +3612,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3729,14 +3729,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3759,33 +3759,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3840,8 +3840,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3850,39 +3852,41 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3905,33 +3909,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 631,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>73</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,1%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3941,19 +3945,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4014,21 +4018,21 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4051,33 +4055,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 631,00</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,0%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4094,12 +4098,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4167,14 +4171,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4197,33 +4201,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,5%</t>
+        <v>80</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4240,14 +4244,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4270,7 +4274,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4278,10 +4282,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4290,41 +4292,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4347,33 +4347,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>62</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4390,14 +4390,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4428,8 +4428,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4438,39 +4440,41 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4493,33 +4497,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,6%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,6%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4536,12 +4540,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,14 +4613,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4639,33 +4643,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 4,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4682,14 +4686,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4712,7 +4716,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4720,10 +4724,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4732,41 +4734,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4789,33 +4789,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>65</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,14 +4832,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4870,8 +4870,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4880,39 +4882,41 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4935,7 +4939,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4944,24 +4948,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,3%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4978,12 +4982,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5019,9 +5023,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5051,14 +5055,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5084,17 +5088,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,1%</t>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5124,14 +5128,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5163,11 +5167,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5197,14 +5201,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5227,33 +5231,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 19,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,1%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5270,14 +5274,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5309,11 +5313,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5343,14 +5347,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5373,33 +5377,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▲ 19,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5416,14 +5420,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5455,11 +5459,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5489,14 +5493,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5528,16 +5532,16 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,0%</t>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5545,7 +5549,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5562,12 +5566,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5605,7 +5609,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5635,14 +5639,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5668,22 +5672,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,2%</t>
+        <v>46</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5691,7 +5695,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5708,14 +5712,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5738,7 +5742,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5746,10 +5750,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5758,41 +5760,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5815,33 +5815,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,4%</t>
+        <v>43</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5858,14 +5858,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5896,8 +5896,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5906,39 +5908,41 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5961,33 +5965,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>56</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6004,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6045,9 +6049,9 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6077,14 +6081,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6110,22 +6114,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>45</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6150,14 +6154,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6189,11 +6193,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6223,14 +6227,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6253,33 +6257,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6296,14 +6300,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6335,11 +6339,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6369,14 +6373,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6399,33 +6403,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+        <v>35</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6442,14 +6446,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6481,11 +6485,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6515,14 +6519,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6545,33 +6549,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,2%</t>
+        <v>31</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6588,14 +6592,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6627,11 +6631,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6661,14 +6665,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6691,33 +6695,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+        <v>54</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6734,12 +6738,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6807,14 +6811,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6837,33 +6841,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,8%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6880,12 +6884,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6953,14 +6957,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6983,7 +6987,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6992,24 +6996,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,0%</t>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7026,12 +7030,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7069,7 +7073,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7099,14 +7103,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7138,11 +7142,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7172,14 +7176,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7202,7 +7206,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7210,10 +7214,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7222,41 +7224,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7282,17 +7282,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7399,14 +7399,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7429,33 +7429,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,5%</t>
+        <v>70</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7472,14 +7472,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7510,8 +7510,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7520,39 +7522,41 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7578,22 +7582,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>52</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7601,7 +7605,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7618,12 +7622,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7659,9 +7663,9 @@
       <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7691,14 +7695,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7721,33 +7725,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7764,14 +7768,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7803,11 +7807,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7837,14 +7841,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7867,7 +7871,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7876,24 +7880,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7910,14 +7914,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7949,11 +7953,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7983,14 +7987,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8016,17 +8020,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8056,14 +8060,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8086,7 +8090,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8094,10 +8098,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8106,41 +8108,39 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8163,33 +8163,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8206,14 +8206,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8244,8 +8244,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
-        <v>0</v>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8254,39 +8256,41 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8309,33 +8313,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,6%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8352,12 +8356,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8393,9 +8397,9 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8425,14 +8429,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8455,33 +8459,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,0%</t>
+        <v>63</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8498,14 +8502,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8537,11 +8541,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8571,14 +8575,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8604,22 +8608,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>87</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
@@ -8627,7 +8631,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8644,14 +8648,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8683,11 +8687,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8717,14 +8721,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8747,33 +8751,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>77</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8783,21 +8787,21 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8829,11 +8833,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8856,21 +8860,21 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8893,33 +8897,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8936,14 +8940,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8975,11 +8979,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9009,14 +9013,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9039,33 +9043,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>102</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9082,14 +9086,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9112,7 +9116,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9120,10 +9124,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9132,41 +9134,39 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9189,33 +9189,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+        <v>93</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9232,14 +9232,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9270,8 +9270,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="n">
-        <v>0</v>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9280,39 +9282,41 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9338,22 +9342,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>121</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
@@ -9361,7 +9365,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9378,12 +9382,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9451,14 +9455,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9481,33 +9485,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>81</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9524,14 +9528,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9554,7 +9558,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9562,10 +9566,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9574,41 +9576,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9631,33 +9631,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>87</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9751,14 +9751,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9784,22 +9784,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9824,12 +9824,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9901,14 +9901,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9931,33 +9931,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+        <v>84</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10051,14 +10051,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10081,33 +10081,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>89</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10201,14 +10201,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10274,12 +10274,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10392,9 +10392,9 @@
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10424,12 +10424,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10501,14 +10501,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10536,20 +10536,20 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10574,12 +10574,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10651,14 +10651,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10681,33 +10681,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>48</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10724,12 +10724,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10801,14 +10801,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10831,33 +10831,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>67</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10874,12 +10874,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10951,14 +10951,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10981,33 +10981,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>36</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11101,14 +11101,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11140,24 +11140,24 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11251,14 +11251,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11284,17 +11284,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,2%</t>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11401,14 +11401,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11431,33 +11431,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11551,14 +11551,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11581,33 +11581,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>49</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11624,12 +11624,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11701,14 +11701,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11731,33 +11731,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,8%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11774,12 +11774,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11851,14 +11851,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11881,25 +11881,25 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>44</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12001,14 +12001,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12034,17 +12034,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,0%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12074,12 +12074,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12151,14 +12151,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12181,33 +12181,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,4%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12224,12 +12224,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12301,14 +12301,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12331,33 +12331,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>33</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M160" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12374,12 +12374,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12451,14 +12451,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12484,17 +12484,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12601,14 +12601,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12631,33 +12631,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12751,14 +12751,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12781,33 +12781,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>36</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12824,12 +12824,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12901,14 +12901,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12931,33 +12931,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12974,82 +12974,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,37 +609,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -782,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +863,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -892,17 +896,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1013,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1039,33 +1043,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1163,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1189,7 +1193,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1198,24 +1202,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 118,8%</t>
+        <v>13</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1236,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1313,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1348,11 +1352,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>35</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 118,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1386,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1463,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1498,7 +1502,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1532,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1613,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1642,17 +1646,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1763,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1789,33 +1793,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1836,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1913,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1939,33 +1943,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2063,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2094,20 +2098,20 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,3%</t>
+        <v>77</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2115,7 +2119,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2136,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2213,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2239,33 +2243,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+        <v>54</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2286,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2363,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2389,33 +2393,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 390,9%</t>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2436,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2513,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2544,20 +2548,20 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>54</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 390,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2565,7 +2569,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2586,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2663,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2689,7 +2693,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2697,10 +2701,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2709,39 +2711,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,14 +2813,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2851,8 +2851,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2861,37 +2863,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2963,14 +2967,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2993,7 +2997,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3001,10 +3005,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3013,39 +3015,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3579,14 +3579,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3617,8 +3617,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3627,37 +3629,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3729,14 +3733,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3762,17 +3766,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3802,12 +3806,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3879,14 +3883,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3909,33 +3913,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3952,14 +3956,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3982,7 +3986,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3990,8 +3994,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4000,39 +4006,41 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4055,33 +4063,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 631,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>73</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,1%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4091,19 +4099,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4164,21 +4172,21 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4201,33 +4209,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 631,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,0%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4244,12 +4252,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4317,14 +4325,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4347,33 +4355,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,5%</t>
+        <v>80</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4390,14 +4398,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4420,7 +4428,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4428,10 +4436,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4440,41 +4446,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4497,33 +4501,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>62</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,5%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4540,14 +4544,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4570,7 +4574,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4578,8 +4582,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4588,39 +4594,41 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4643,33 +4651,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,6%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,6%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4686,12 +4694,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,14 +4767,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4789,33 +4797,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 4,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,14 +4840,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4862,7 +4870,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4870,10 +4878,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4882,41 +4888,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4939,33 +4943,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>65</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4982,14 +4986,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5012,7 +5016,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5020,8 +5024,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5030,39 +5036,41 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5085,7 +5093,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5094,24 +5102,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,3%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5128,12 +5136,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5169,9 +5177,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5201,14 +5209,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5234,17 +5242,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,1%</t>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5274,14 +5282,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5313,11 +5321,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5347,14 +5355,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5377,33 +5385,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 19,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5420,14 +5428,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5459,11 +5467,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5493,14 +5501,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5523,33 +5531,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▲ 19,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5566,14 +5574,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5605,11 +5613,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5639,14 +5647,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5678,16 +5686,16 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,0%</t>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5695,7 +5703,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5712,12 +5720,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5755,7 +5763,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5785,14 +5793,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5818,22 +5826,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,2%</t>
+        <v>46</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5841,7 +5849,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5858,14 +5866,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5888,7 +5896,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5896,10 +5904,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5908,41 +5914,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5965,33 +5969,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,4%</t>
+        <v>43</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6008,14 +6012,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6038,7 +6042,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6046,8 +6050,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6056,39 +6062,41 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6111,33 +6119,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>56</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6154,12 +6162,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6195,9 +6203,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6227,14 +6235,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6260,22 +6268,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>45</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6300,14 +6308,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6339,11 +6347,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6373,14 +6381,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6403,33 +6411,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6446,14 +6454,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6485,11 +6493,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6519,14 +6527,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6549,33 +6557,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+        <v>35</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6592,14 +6600,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6631,11 +6639,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6665,14 +6673,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6695,33 +6703,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,2%</t>
+        <v>31</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6738,14 +6746,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6777,11 +6785,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6811,14 +6819,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6841,33 +6849,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+        <v>54</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6884,12 +6892,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6957,14 +6965,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6987,33 +6995,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,8%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7030,12 +7038,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7103,14 +7111,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7133,7 +7141,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7142,24 +7150,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,0%</t>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7176,12 +7184,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7219,7 +7227,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7249,14 +7257,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7288,11 +7296,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7322,14 +7330,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7352,7 +7360,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7360,10 +7368,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7372,41 +7378,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7432,17 +7436,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7472,12 +7476,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7549,14 +7553,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7579,33 +7583,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,5%</t>
+        <v>70</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7622,14 +7626,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7652,7 +7656,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7660,8 +7664,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7670,39 +7676,41 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7728,22 +7736,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>52</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7751,7 +7759,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7768,12 +7776,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7809,9 +7817,9 @@
       <c r="I99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7841,14 +7849,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7871,33 +7879,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7914,14 +7922,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7953,11 +7961,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7987,14 +7995,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8017,7 +8025,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8026,24 +8034,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8060,14 +8068,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8099,11 +8107,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8133,14 +8141,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8166,17 +8174,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8206,14 +8214,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8236,7 +8244,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8244,10 +8252,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8256,41 +8262,39 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8313,33 +8317,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8356,14 +8360,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8386,7 +8390,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8394,8 +8398,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8404,39 +8410,41 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8459,33 +8467,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,6%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8502,12 +8510,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8543,9 +8551,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8575,14 +8583,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8605,33 +8613,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,0%</t>
+        <v>63</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8648,14 +8656,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8687,11 +8695,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8721,14 +8729,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8754,22 +8762,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>87</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
@@ -8777,7 +8785,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8794,14 +8802,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8833,11 +8841,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8867,14 +8875,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8897,33 +8905,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>77</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8933,21 +8941,21 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8979,11 +8987,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9006,21 +9014,21 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9043,33 +9051,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9086,14 +9094,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9125,11 +9133,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9159,14 +9167,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9189,33 +9197,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>102</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9232,14 +9240,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9262,7 +9270,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9270,10 +9278,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9282,41 +9288,39 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9339,33 +9343,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+        <v>93</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9382,14 +9386,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9412,7 +9416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9420,8 +9424,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9430,39 +9436,41 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9488,22 +9496,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>121</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
@@ -9511,7 +9519,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9528,12 +9536,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9601,14 +9609,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9631,33 +9639,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>81</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9674,14 +9682,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9704,7 +9712,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9712,10 +9720,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9724,41 +9730,39 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9781,33 +9785,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>87</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9824,12 +9828,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9901,14 +9905,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9934,22 +9938,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
@@ -9957,7 +9961,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9974,12 +9978,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10051,14 +10055,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10081,33 +10085,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+        <v>84</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10124,12 +10128,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10201,14 +10205,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10231,33 +10235,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>89</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10274,12 +10278,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10351,14 +10355,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10390,7 +10394,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10399,7 +10403,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
@@ -10407,7 +10411,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10424,12 +10428,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10501,12 +10505,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10542,9 +10546,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10557,7 +10561,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10574,12 +10578,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10651,14 +10655,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10686,20 +10690,20 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
@@ -10707,7 +10711,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10724,12 +10728,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10801,14 +10805,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10831,33 +10835,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>48</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10874,12 +10878,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10951,14 +10955,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10981,33 +10985,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>67</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11024,12 +11028,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11101,14 +11105,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11131,33 +11135,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>36</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11174,12 +11178,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11251,14 +11255,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11281,7 +11285,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11290,24 +11294,24 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11324,12 +11328,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11401,14 +11405,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11434,17 +11438,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,2%</t>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11474,12 +11478,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11551,14 +11555,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11581,33 +11585,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11624,12 +11628,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11701,14 +11705,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11731,33 +11735,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>49</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11774,12 +11778,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11851,14 +11855,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11881,33 +11885,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,8%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11924,12 +11928,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12001,14 +12005,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12031,25 +12035,25 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>44</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
@@ -12057,7 +12061,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12074,12 +12078,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12151,14 +12155,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12184,17 +12188,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,0%</t>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12224,12 +12228,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12301,14 +12305,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12331,33 +12335,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,4%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12374,12 +12378,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12451,14 +12455,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12481,33 +12485,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>33</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M162" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12524,12 +12528,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12601,14 +12605,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12634,17 +12638,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12657,7 +12661,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12674,12 +12678,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12751,14 +12755,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12781,33 +12785,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12824,12 +12828,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12901,14 +12905,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12931,33 +12935,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>36</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12974,12 +12978,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13051,14 +13055,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -13081,33 +13085,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13124,82 +13128,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,14 +713,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -743,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,8 +751,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -761,37 +763,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -863,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +940,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1013,14 +1017,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1046,17 +1050,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1086,12 +1090,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1163,14 +1167,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1193,33 +1197,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1236,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1313,14 +1317,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1343,7 +1347,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1352,24 +1356,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 118,8%</t>
+        <v>13</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1386,12 +1390,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1463,14 +1467,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1502,11 +1506,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>35</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 118,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1536,12 +1540,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,14 +1617,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1652,7 +1656,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1686,12 +1690,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,14 +1767,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1796,17 +1800,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1836,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,14 +1917,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -1943,33 +1947,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1986,12 +1990,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,14 +2067,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2093,33 +2097,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2136,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,14 +2217,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2248,20 +2252,20 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,3%</t>
+        <v>77</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2269,7 +2273,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2286,12 +2290,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2363,14 +2367,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2393,33 +2397,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+        <v>54</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2436,12 +2440,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,14 +2517,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2543,33 +2547,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 390,9%</t>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2586,12 +2590,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2663,14 +2667,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2698,20 +2702,20 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>54</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 390,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2736,12 +2740,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,14 +2817,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2843,7 +2847,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2851,10 +2855,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2863,39 +2865,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2967,14 +2967,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3005,8 +3005,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3015,37 +3017,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3117,14 +3121,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3147,7 +3151,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3155,10 +3159,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3167,39 +3169,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3733,14 +3733,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3771,8 +3771,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3781,37 +3783,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3883,14 +3887,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -3916,17 +3920,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3956,12 +3960,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4033,14 +4037,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4063,33 +4067,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4106,14 +4110,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4136,7 +4140,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4144,8 +4148,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4154,39 +4160,41 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4209,33 +4217,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 631,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>73</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,1%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4245,19 +4253,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4318,21 +4326,21 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4355,33 +4363,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 631,00</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 29,0%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4398,12 +4406,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4471,14 +4479,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4501,33 +4509,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,5%</t>
+        <v>80</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4544,14 +4552,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4574,7 +4582,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4582,10 +4590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4594,41 +4600,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4651,33 +4655,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,9%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>62</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4694,14 +4698,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4724,7 +4728,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4732,8 +4736,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4742,39 +4748,41 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4797,33 +4805,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,6%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,6%</t>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4840,12 +4848,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4913,14 +4921,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -4943,33 +4951,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 4,6%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4986,14 +4994,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5016,7 +5024,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5024,10 +5032,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5036,41 +5042,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5093,33 +5097,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,3%</t>
+        <v>65</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5136,14 +5140,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5166,7 +5170,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5174,8 +5178,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5184,39 +5190,41 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5239,7 +5247,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5248,24 +5256,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,3%</t>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5282,12 +5290,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5323,9 +5331,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5355,14 +5363,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5388,17 +5396,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,1%</t>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5428,14 +5436,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5467,11 +5475,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5501,14 +5509,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5531,33 +5539,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 19,2%</t>
+        <v>57</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,1%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5574,14 +5582,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5613,11 +5621,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5647,14 +5655,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5677,33 +5685,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▲ 19,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5720,14 +5728,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5759,11 +5767,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5793,14 +5801,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5832,16 +5840,16 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,0%</t>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5849,7 +5857,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5866,12 +5874,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5909,7 +5917,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5939,14 +5947,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -5972,22 +5980,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,2%</t>
+        <v>46</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5995,7 +6003,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6012,14 +6020,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6042,7 +6050,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6050,10 +6058,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6062,41 +6068,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6119,33 +6123,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,4%</t>
+        <v>43</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6162,14 +6166,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6192,7 +6196,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6200,8 +6204,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6210,39 +6216,41 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6265,33 +6273,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>56</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6308,12 +6316,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6349,9 +6357,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6381,14 +6389,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6414,22 +6422,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>45</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6454,14 +6462,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6493,11 +6501,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6527,14 +6535,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6557,33 +6565,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6600,14 +6608,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6639,11 +6647,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6673,14 +6681,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6703,33 +6711,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+        <v>35</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6746,14 +6754,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6785,11 +6793,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6819,14 +6827,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6849,33 +6857,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,2%</t>
+        <v>31</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6892,14 +6900,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6931,11 +6939,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6965,14 +6973,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -6995,33 +7003,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+        <v>54</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7038,12 +7046,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7111,14 +7119,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7141,33 +7149,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,8%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7184,12 +7192,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7257,14 +7265,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7287,7 +7295,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7296,24 +7304,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,0%</t>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7330,12 +7338,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7373,7 +7381,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7403,14 +7411,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7442,11 +7450,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,3%</t>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7476,14 +7484,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7506,7 +7514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7514,10 +7522,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7526,41 +7532,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7586,17 +7590,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>53</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7626,12 +7630,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7703,14 +7707,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7733,33 +7737,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,5%</t>
+        <v>70</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7776,14 +7780,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7806,7 +7810,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7814,8 +7818,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7824,39 +7830,41 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -7882,22 +7890,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>52</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -7905,7 +7913,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7922,12 +7930,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7963,9 +7971,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7995,14 +8003,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8025,33 +8033,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8068,14 +8076,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8107,11 +8115,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8141,14 +8149,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8171,7 +8179,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8180,24 +8188,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8214,14 +8222,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8253,11 +8261,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8287,14 +8295,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8320,17 +8328,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8360,14 +8368,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8390,7 +8398,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8398,10 +8406,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8410,41 +8416,39 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8467,33 +8471,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8510,14 +8514,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8540,7 +8544,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8548,8 +8552,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8558,39 +8564,41 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8613,33 +8621,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,6%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8656,12 +8664,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8697,9 +8705,9 @@
       <c r="I111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8729,14 +8737,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8759,33 +8767,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,0%</t>
+        <v>63</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8802,14 +8810,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8841,11 +8849,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8875,14 +8883,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8908,22 +8916,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>87</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
@@ -8931,7 +8939,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8948,14 +8956,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -8987,11 +8995,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9021,14 +9029,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9051,33 +9059,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>77</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9087,21 +9095,21 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9133,11 +9141,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9160,21 +9168,21 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9197,33 +9205,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 9,7%</t>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9240,14 +9248,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9279,11 +9287,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9313,14 +9321,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9343,33 +9351,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>102</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9386,14 +9394,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9416,7 +9424,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9424,10 +9432,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9436,41 +9442,39 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9493,33 +9497,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+        <v>93</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9536,14 +9540,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9566,7 +9570,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9574,8 +9578,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9584,39 +9590,41 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9642,22 +9650,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>121</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
@@ -9665,7 +9673,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9682,12 +9690,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9755,14 +9763,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9785,33 +9793,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,8%</t>
+        <v>81</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9828,14 +9836,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9858,7 +9866,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9866,10 +9874,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9878,41 +9884,39 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -9935,33 +9939,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>87</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9978,12 +9982,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10055,14 +10059,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10088,22 +10092,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
@@ -10111,7 +10115,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10128,12 +10132,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10205,14 +10209,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10235,33 +10239,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+        <v>84</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10278,12 +10282,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10355,14 +10359,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10385,33 +10389,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>89</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10428,12 +10432,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10505,14 +10509,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10544,7 +10548,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10553,7 +10557,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
@@ -10561,7 +10565,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10578,12 +10582,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10655,12 +10659,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10696,9 +10700,9 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10711,7 +10715,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10728,12 +10732,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10805,14 +10809,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10840,20 +10844,20 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
@@ -10861,7 +10865,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10878,12 +10882,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10955,14 +10959,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -10985,33 +10989,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>48</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11028,12 +11032,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11105,14 +11109,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11135,33 +11139,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>67</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11178,12 +11182,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11255,14 +11259,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11285,33 +11289,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>36</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11328,12 +11332,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11405,14 +11409,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11435,7 +11439,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11444,24 +11448,24 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,4%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11478,12 +11482,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11555,14 +11559,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11588,17 +11592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,2%</t>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11628,12 +11632,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11705,14 +11709,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11735,33 +11739,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,1%</t>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11778,12 +11782,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11855,14 +11859,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -11885,33 +11889,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>49</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11928,12 +11932,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12005,14 +12009,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12035,33 +12039,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,8%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12078,12 +12082,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12155,14 +12159,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12185,25 +12189,25 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>44</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12211,7 +12215,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12228,12 +12232,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12305,14 +12309,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12338,17 +12342,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,0%</t>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12378,12 +12382,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12455,14 +12459,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12485,33 +12489,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,4%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12528,12 +12532,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12605,14 +12609,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12635,33 +12639,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>33</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M164" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12678,12 +12682,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12755,14 +12759,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12788,17 +12792,17 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12811,7 +12815,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12828,12 +12832,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12905,14 +12909,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -12935,33 +12939,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12978,12 +12982,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13055,14 +13059,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -13085,33 +13089,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,1%</t>
+        <v>36</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13128,12 +13132,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13205,14 +13209,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-025-BR</t>
@@ -13235,33 +13239,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13278,82 +13282,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-025-BR-CARRINHO-PRATELEIRA-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,10 +751,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -763,39 +761,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -900,9 +896,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -933,19 +929,19 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,12 +1013,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1047,7 +1043,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1069,11 +1065,11 @@
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1083,19 +1079,19 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1167,12 +1163,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1197,55 +1193,59 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1355,47 +1355,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,9%</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1467,12 +1471,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1506,11 +1510,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 118,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1540,12 +1544,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1617,12 +1621,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1656,7 +1660,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1690,12 +1694,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1767,12 +1771,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,17 +1804,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1840,12 +1844,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1917,12 +1921,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1947,33 +1951,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 62,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1990,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2067,12 +2071,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2097,33 +2101,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 118,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2140,12 +2144,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2217,12 +2221,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2247,33 +2251,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,6%</t>
+        <v>16</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2290,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2367,12 +2371,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2397,7 +2401,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2406,24 +2410,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2440,12 +2444,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2517,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2556,11 +2560,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2590,12 +2594,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2667,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2700,22 +2704,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 390,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2723,7 +2727,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2740,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2817,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2847,33 +2851,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>77</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2890,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2967,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2997,7 +3001,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3005,51 +3009,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I34" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3121,12 +3121,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3154,17 +3154,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>57</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3301,59 +3301,55 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 390,9%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3425,12 +3421,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3455,7 +3451,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3463,10 +3459,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3475,39 +3469,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3579,12 +3571,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3656,12 +3648,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3733,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3763,7 +3755,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3771,10 +3763,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3783,39 +3773,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3887,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3917,7 +3905,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3925,8 +3913,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3935,37 +3925,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4037,12 +4029,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4067,55 +4059,59 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4187,12 +4183,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4217,55 +4213,59 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,9%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,1%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4298,8 +4298,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4308,37 +4310,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4363,55 +4367,59 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 631,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>7</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4436,7 +4444,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4444,8 +4452,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4454,37 +4464,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4509,33 +4521,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 29,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4545,19 +4557,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4582,7 +4594,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4590,8 +4602,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4600,37 +4614,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4655,33 +4671,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4691,19 +4707,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4775,12 +4791,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4805,7 +4821,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -4814,26 +4830,26 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,7%</t>
+        <v>73</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,1%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
           <t>3,8%</t>
         </is>
       </c>
-      <c r="L58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
@@ -4841,19 +4857,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4914,19 +4930,19 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4951,33 +4967,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 473,00</t>
+          <t>R$ 631,00</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,6%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,6%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4994,12 +5010,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5067,12 +5083,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5097,33 +5113,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,7%</t>
+          <t>▲ 29,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5140,12 +5156,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5170,7 +5186,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5178,10 +5194,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5190,39 +5204,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5247,33 +5259,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,3%</t>
+          <t>▼ 20,5%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5290,12 +5302,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5320,7 +5332,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5328,8 +5340,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5338,37 +5352,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5393,33 +5409,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,9%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,3%</t>
+        <v>78</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5436,12 +5452,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5477,9 +5493,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5509,12 +5525,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5539,33 +5555,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 473,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,6%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,1%</t>
+        <v>68</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5582,12 +5598,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5621,7 +5637,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5655,12 +5671,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5685,33 +5701,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,2%</t>
+          <t>▲ 32,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5728,12 +5744,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5758,7 +5774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5766,47 +5782,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5831,33 +5851,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 395,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 13,0%</t>
+        <v>49</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5874,12 +5894,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5913,11 +5933,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5947,12 +5967,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5977,33 +5997,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,0%</t>
+        <v>54</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6020,12 +6040,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6059,11 +6079,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6093,12 +6113,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6123,33 +6143,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,2%</t>
+          <t>▼ 8,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6166,12 +6186,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6196,7 +6216,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6204,10 +6224,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6216,39 +6234,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6273,33 +6289,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,4%</t>
+          <t>▲ 19,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6316,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6357,9 +6373,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6389,12 +6405,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6428,16 +6444,16 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>52</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6462,12 +6478,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6501,11 +6517,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6535,12 +6551,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6568,22 +6584,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>46</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6591,7 +6607,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6608,12 +6624,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6647,11 +6663,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6681,12 +6697,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6711,33 +6727,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>43</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6754,12 +6770,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6784,7 +6800,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6792,8 +6808,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>5</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6802,37 +6820,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6857,33 +6877,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,6%</t>
+        <v>56</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,4%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6900,12 +6920,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6941,9 +6961,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6973,12 +6993,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7008,20 +7028,20 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 74,2%</t>
+        <v>45</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -7029,7 +7049,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7046,12 +7066,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7085,11 +7105,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7119,12 +7139,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7149,33 +7169,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
-        </is>
-      </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7192,12 +7212,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7231,11 +7251,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7265,12 +7285,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7304,16 +7324,16 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,8%</t>
+        <v>35</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7338,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7377,11 +7397,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7411,12 +7431,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7444,17 +7464,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,0%</t>
+          <t>▼ 42,6%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7484,12 +7504,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7523,11 +7543,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7557,12 +7577,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7587,7 +7607,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7596,24 +7616,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,3%</t>
+        <v>54</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 74,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7630,12 +7650,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7660,7 +7680,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7668,51 +7688,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7746,11 +7762,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,6%</t>
+        <v>31</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7780,12 +7796,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7810,7 +7826,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7818,51 +7834,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7892,20 +7904,20 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,5%</t>
+          <t>▼ 6,8%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -7913,7 +7925,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7930,12 +7942,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7969,11 +7981,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8003,12 +8015,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8033,33 +8045,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>44</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8076,12 +8088,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8115,11 +8127,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8149,12 +8161,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8179,7 +8191,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8188,24 +8200,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+        <v>53</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,3%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8222,12 +8234,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8252,7 +8264,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8260,47 +8272,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8328,17 +8344,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 34,6%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8368,12 +8384,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8398,7 +8414,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8406,8 +8422,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>2</v>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8416,37 +8434,39 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8471,33 +8491,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>52</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,5%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8514,12 +8534,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8544,7 +8564,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8552,10 +8572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8564,39 +8582,37 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8626,20 +8642,20 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>63</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
@@ -8647,7 +8663,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8664,12 +8680,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8705,9 +8721,9 @@
       <c r="I111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8737,12 +8753,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8767,33 +8783,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,6%</t>
+        <v>49</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8810,12 +8826,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8849,11 +8865,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8883,12 +8899,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8913,33 +8929,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 13,0%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8956,12 +8972,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8995,11 +9011,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9029,12 +9045,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9059,33 +9075,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9102,12 +9118,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9132,7 +9148,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9140,8 +9156,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="n">
-        <v>2</v>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9150,37 +9168,39 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9210,20 +9230,20 @@
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
@@ -9231,7 +9251,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9241,19 +9261,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9289,9 +9309,9 @@
       <c r="I119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9314,19 +9334,19 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9351,33 +9371,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 9,7%</t>
+        <v>63</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,6%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9387,19 +9407,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9433,11 +9453,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9460,19 +9480,19 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9497,33 +9517,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>87</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 13,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9533,19 +9553,19 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9570,7 +9590,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9578,51 +9598,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9650,22 +9666,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+        <v>77</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
@@ -9673,7 +9689,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9683,19 +9699,19 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9729,7 +9745,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9756,19 +9772,19 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9793,33 +9809,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,9%</t>
+        <v>112</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 9,8%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9836,12 +9852,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9877,9 +9893,9 @@
       <c r="I127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9909,12 +9925,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9939,33 +9955,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,8%</t>
+          <t>▲ 9,7%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9982,12 +9998,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10012,7 +10028,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10020,10 +10036,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10032,39 +10046,37 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10089,33 +10101,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,8%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10132,12 +10144,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10209,12 +10221,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10242,22 +10254,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>121</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
@@ -10265,7 +10277,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10282,12 +10294,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10312,7 +10324,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10320,10 +10332,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10332,39 +10342,37 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10389,33 +10397,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,9%</t>
+        <v>81</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,9%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10432,12 +10440,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10462,7 +10470,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10470,10 +10478,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10482,39 +10488,37 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10539,33 +10543,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>87</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,8%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10582,12 +10586,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10659,12 +10663,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10698,16 +10702,16 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>80</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
@@ -10715,7 +10719,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10732,12 +10736,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10809,12 +10813,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10842,22 +10846,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
@@ -10865,7 +10869,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10882,12 +10886,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10959,12 +10963,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10989,33 +10993,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,4%</t>
+        <v>89</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,9%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11032,12 +11036,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11109,12 +11113,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11139,33 +11143,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 86,1%</t>
+        <v>65</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11182,12 +11186,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11259,12 +11263,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11289,33 +11293,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 395,00</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11332,12 +11336,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11409,12 +11413,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11444,20 +11448,20 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
@@ -11465,7 +11469,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11482,12 +11486,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11559,12 +11563,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11589,7 +11593,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11598,24 +11602,24 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,4%</t>
+        <v>48</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,4%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11632,12 +11636,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11709,12 +11713,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11748,11 +11752,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,2%</t>
+          <t>▲ 86,1%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11782,12 +11786,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11859,12 +11863,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11889,33 +11893,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 395,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 44,1%</t>
+        <v>36</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,6%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11932,12 +11936,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12009,12 +12013,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12039,33 +12043,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,7%</t>
+        <v>65</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12082,12 +12086,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12159,12 +12163,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12189,33 +12193,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 16,4%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12232,12 +12236,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12309,12 +12313,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12339,33 +12343,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>55</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,2%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12382,12 +12386,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12459,12 +12463,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12489,25 +12493,25 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,8%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 3,0%</t>
+        <v>49</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,1%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
@@ -12515,7 +12519,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12532,12 +12536,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12609,12 +12613,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12639,25 +12643,25 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▲ 201,4%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 22,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
@@ -12665,7 +12669,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12682,12 +12686,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12759,12 +12763,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12789,25 +12793,25 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,8%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>44</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
@@ -12815,7 +12819,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12832,12 +12836,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12909,12 +12913,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12942,22 +12946,22 @@
           <t>R$ 74,00</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>32</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -12982,12 +12986,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13059,12 +13063,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13089,33 +13093,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,1%</t>
+        <v>32</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 3,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13132,12 +13136,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13209,12 +13213,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13239,33 +13243,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,8%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,4%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,1%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13282,12 +13286,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13359,12 +13363,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13389,33 +13393,33 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 74,00</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13432,82 +13436,682 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 148,00</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,1%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,8%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,1%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4502626841</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-025-BR</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Carrinho prateleira branco</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4502665317</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-025-BR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Carrinho prateleira branco</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4502626841</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>